--- a/xls/square_16_quad4_10.xlsx
+++ b/xls/square_16_quad4_10.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>289</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>192</v>
+      </c>
+      <c r="I8">
+        <v>5.322183675678701</v>
+      </c>
+      <c r="J8">
+        <v>4.3025570358227805</v>
+      </c>
+      <c r="K8">
+        <v>1.812641245220425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>289</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>243</v>
+      </c>
+      <c r="I9">
+        <v>2.54211456461116</v>
+      </c>
+      <c r="J9">
+        <v>0.6508987702446074</v>
+      </c>
+      <c r="K9">
+        <v>0.6225172475417641</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>300</v>
       </c>
       <c r="I10">
-        <v>3.6484276535532953</v>
+        <v>2.2568676863819888</v>
       </c>
       <c r="J10">
-        <v>0.9821494981493621</v>
+        <v>-0.3598468085801969</v>
       </c>
       <c r="K10">
-        <v>0.7303925340999584</v>
+        <v>0.3327974108231401</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -517,13 +587,13 @@
         <v>363</v>
       </c>
       <c r="I11">
-        <v>-1.4067136227381294</v>
+        <v>-1.0861421495342207</v>
       </c>
       <c r="J11">
-        <v>-1.2901521758797543</v>
+        <v>-1.1147844764633048</v>
       </c>
       <c r="K11">
-        <v>-1.0674380919627016</v>
+        <v>-1.0633445062445575</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -552,13 +622,13 @@
         <v>432</v>
       </c>
       <c r="I12">
-        <v>-1.475313017956975</v>
+        <v>-1.1658330995524628</v>
       </c>
       <c r="J12">
-        <v>-1.4641205957409211</v>
+        <v>-1.207393600542535</v>
       </c>
       <c r="K12">
-        <v>-1.1625817403008176</v>
+        <v>-1.1543640871563574</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -587,13 +657,13 @@
         <v>507</v>
       </c>
       <c r="I13">
-        <v>-1.5619277000262288</v>
+        <v>-1.2417671784110615</v>
       </c>
       <c r="J13">
-        <v>-1.5655420192270044</v>
+        <v>-1.2868884188786824</v>
       </c>
       <c r="K13">
-        <v>-0.994196594057957</v>
+        <v>-1.0652259054217055</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -622,13 +692,13 @@
         <v>588</v>
       </c>
       <c r="I14">
-        <v>-1.6246367198799996</v>
+        <v>-1.3002459036863327</v>
       </c>
       <c r="J14">
-        <v>-1.6541438517125737</v>
+        <v>-1.3484820208574653</v>
       </c>
       <c r="K14">
-        <v>-1.0440307455358826</v>
+        <v>-1.0687962796891137</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -657,13 +727,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>-1.7816344768943158</v>
+        <v>-1.4003187824976517</v>
       </c>
       <c r="J15">
-        <v>-1.5105868872619523</v>
+        <v>-1.3856235658287175</v>
       </c>
       <c r="K15">
-        <v>-0.381979629496842</v>
+        <v>-0.4926328251085813</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -692,13 +762,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.794150412558778</v>
+        <v>-1.5136630313143498</v>
       </c>
       <c r="J16">
-        <v>-1.32411104556103</v>
+        <v>-1.361312756740358</v>
       </c>
       <c r="K16">
-        <v>-0.15916223757249542</v>
+        <v>-0.2630257593444108</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -727,13 +797,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-0.2511437321845974</v>
+        <v>-0.4863609912854767</v>
       </c>
       <c r="J17">
-        <v>-0.20819632641318464</v>
+        <v>-0.3686147618309394</v>
       </c>
       <c r="K17">
-        <v>3.8150556830863533</v>
+        <v>3.5935854982585544</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -762,13 +832,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-0.1464069622577151</v>
+        <v>-0.0037689245148132978</v>
       </c>
       <c r="J18">
-        <v>-0.14020261091035113</v>
+        <v>-0.004105695552264633</v>
       </c>
       <c r="K18">
-        <v>3.8733239653111484</v>
+        <v>4.1749581177357635</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-0.011380066221394543</v>
+        <v>-2.8181739185795496e-5</v>
       </c>
       <c r="J19">
-        <v>-0.014359781910519091</v>
+        <v>-0.00011528987978540946</v>
       </c>
       <c r="K19">
-        <v>3.4818086227707776</v>
+        <v>3.5355614332352334</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-0.00693652375933414</v>
+        <v>-9.186447171494866e-5</v>
       </c>
       <c r="J20">
-        <v>-0.005997260672937479</v>
+        <v>-8.027975639819498e-5</v>
       </c>
       <c r="K20">
-        <v>3.295482851317479</v>
+        <v>3.295051809113616</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -867,13 +937,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-0.0011548737157730925</v>
+        <v>-1.4858333228240514e-5</v>
       </c>
       <c r="J21">
-        <v>-0.0009324200023811401</v>
+        <v>-1.2142653481205714e-5</v>
       </c>
       <c r="K21">
-        <v>2.870799158501824</v>
+        <v>2.8734768235549475</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -902,13 +972,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-4.320454104002571e-5</v>
+        <v>-5.094725530205543e-7</v>
       </c>
       <c r="J22">
-        <v>-3.991311521731749e-5</v>
+        <v>-4.6836552811510827e-7</v>
       </c>
       <c r="K22">
-        <v>2.235699053595462</v>
+        <v>2.242789745393906</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.0002062579847831728</v>
+        <v>-2.7587115014790446e-6</v>
       </c>
       <c r="J23">
-        <v>-0.00017442403610724055</v>
+        <v>-2.3428526156255036e-6</v>
       </c>
       <c r="K23">
-        <v>2.5263945541460293</v>
+        <v>2.5710602176056465</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-3.666485393744312e-5</v>
+        <v>-4.926644462440032e-7</v>
       </c>
       <c r="J24">
-        <v>-3.2109057832282156e-5</v>
+        <v>-4.308518879464976e-7</v>
       </c>
       <c r="K24">
-        <v>2.1732373047125866</v>
+        <v>2.212458612445327</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-1.675860474155279e-6</v>
+        <v>-2.7295390474335372e-8</v>
       </c>
       <c r="J25">
-        <v>-3.7030966644103734e-6</v>
+        <v>-4.705887293431674e-8</v>
       </c>
       <c r="K25">
-        <v>1.85366354871681</v>
+        <v>1.8530560820135609</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-4.01179782624765e-5</v>
+        <v>-5.06490809420672e-7</v>
       </c>
       <c r="J26">
-        <v>-3.626901037646963e-5</v>
+        <v>-4.6179369689579607e-7</v>
       </c>
       <c r="K26">
-        <v>2.209235830118651</v>
+        <v>2.2435136214500737</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-9.658711505629202e-7</v>
+        <v>-2.0144783837396084e-8</v>
       </c>
       <c r="J27">
-        <v>-2.037076863315456e-6</v>
+        <v>-2.7728322617753118e-8</v>
       </c>
       <c r="K27">
-        <v>1.7219537252608628</v>
+        <v>1.7140615945815971</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1112,13 +1182,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-7.0162979648439894e-6</v>
+        <v>-6.990391052151225e-8</v>
       </c>
       <c r="J28">
-        <v>-6.347037112263564e-6</v>
+        <v>-6.342779166454028e-8</v>
       </c>
       <c r="K28">
-        <v>1.8315649253901307</v>
+        <v>1.8017021059546485</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1147,13 +1217,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-8.775792240096436e-7</v>
+        <v>-1.5196331600119775e-8</v>
       </c>
       <c r="J29">
-        <v>-1.4260352123605625e-6</v>
+        <v>-1.982172004205454e-8</v>
       </c>
       <c r="K29">
-        <v>1.6205136400875104</v>
+        <v>1.6322848673458203</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1182,13 +1252,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-3.4735180133706086e-6</v>
+        <v>-4.214662905803433e-8</v>
       </c>
       <c r="J30">
-        <v>-3.189842635758659e-6</v>
+        <v>-3.8740528564123835e-8</v>
       </c>
       <c r="K30">
-        <v>1.6871277442913974</v>
+        <v>1.700139019825291</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1217,13 +1287,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-1.5875068426851917e-6</v>
+        <v>-2.1526186712167875e-8</v>
       </c>
       <c r="J31">
-        <v>-1.5664463211251774e-6</v>
+        <v>-2.077571454331109e-8</v>
       </c>
       <c r="K31">
-        <v>1.5547062068853579</v>
+        <v>1.5809131220308372</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1252,13 +1322,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-1.6387293894306306e-6</v>
+        <v>-2.0511335235759576e-8</v>
       </c>
       <c r="J32">
-        <v>-1.5006174006527728e-6</v>
+        <v>-1.8862894840672796e-8</v>
       </c>
       <c r="K32">
-        <v>1.523560204194798</v>
+        <v>1.5470645475818843</v>
       </c>
     </row>
   </sheetData>
